--- a/data/trans_dic/IP31KM01_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM01_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>84,9; 97,48</t>
+          <t>86,59; 98,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86,29; 98,67</t>
+          <t>81,98; 96,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89,25; 97,28</t>
+          <t>87,71; 96,93</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,43%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>88,24; 93,15</t>
+          <t>85,59; 91,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>84,19; 90,97</t>
+          <t>87,65; 92,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87,17; 91,21</t>
+          <t>87,42; 91,15</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,7%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>87,29; 95,11</t>
+          <t>87,07; 94,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87,01; 95,05</t>
+          <t>87,79; 95,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88,59; 94,12</t>
+          <t>88,66; 94,12</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,29%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>88,95; 92,95</t>
+          <t>87,51; 91,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>86,8; 91,59</t>
+          <t>88,41; 92,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>88,51; 91,67</t>
+          <t>88,79; 91,7</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>61</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>49926</t>
+          <t>51201</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>55673</t>
+          <t>41975</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>105598</t>
+          <t>93176</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>45592; 52347</t>
+          <t>46514; 53088</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>50348; 57567</t>
+          <t>37632; 44169</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>99999; 108998</t>
+          <t>87380; 96564</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>565</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>563</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>565</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>410195</t>
+          <t>414049</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>445784</t>
+          <t>382845</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>855979</t>
+          <t>796895</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>398700; 420878</t>
+          <t>399234; 426079</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>425350; 459620</t>
+          <t>372236; 392822</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>834244; 872997</t>
+          <t>779004; 812228</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>206</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>134311</t>
+          <t>152315</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>165869</t>
+          <t>135455</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>300179</t>
+          <t>287770</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>127608; 139042</t>
+          <t>145126; 157992</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>157601; 172179</t>
+          <t>129171; 140005</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>289990; 308067</t>
+          <t>278243; 295367</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>853</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>830</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>853</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>594432</t>
+          <t>617565</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>667324</t>
+          <t>560275</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1261757</t>
+          <t>1177840</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>579685; 605742</t>
+          <t>601064; 631556</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>646433; 682126</t>
+          <t>546112; 572036</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1235964; 1280137</t>
+          <t>1158313; 1196305</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM01_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM01_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que toman una fruta o un zumo natural todos los días (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>95,32%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>91,44%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>93,53%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>86,59; 98,83</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>81,98; 96,22</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>87,71; 96,93</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>88,77%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>90,15%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>89,43%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>85,59; 91,35</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>87,65; 92,5</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>87,42; 91,15</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>91,38%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>92,06%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>91,7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>87,07; 94,78</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>87,79; 95,15</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>88,66; 94,12</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>89,92%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>90,7%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>90,29%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>87,51; 91,95</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>88,41; 92,61</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>88,79; 91,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.9531922365542281</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.9143894618304197</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.9353118737753348</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>51201</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>41975</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>93176</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.8659482616990419</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.8197783604874124</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.8771283356916537</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>46514; 53088</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>37632; 44169</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>87380; 96564</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.9883217668354113</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.9621829596558358</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.9693209118906611</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>565</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>563</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1128</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.8877110515423897</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.9015198678143053</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.8942919154324719</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>414049</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>382845</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>796895</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.8559486521537372</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.8765372751455822</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.8742145609734443</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>399234; 426079</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>372236; 392822</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>779004; 812228</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.9135034392204593</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.9250147837536375</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.9114990463082701</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>421</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.9137862401457466</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.9205887423863627</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.916975652334583</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>152315</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>135455</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>287770</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.8706574174783555</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.8778781679933038</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.8866178614238095</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>145126; 157992</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>129171; 140005</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>278243; 295367</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.947839750887988</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.9515084829733629</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.9411840891815056</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>853</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>830</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1683</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.8991603690392778</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.9070184994451386</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.9028812768443072</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>617565</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>560275</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1177840</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.8751361066392803</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.8840891250322079</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.8879124973759819</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>601064; 631556</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>546112; 572036</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>1158313; 1196305</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.91953108098611</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.9260578346991787</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.9170359326935609</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que toman una fruta o un zumo natural todos los días (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>51201</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>41975</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>93176</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>46514</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>37632</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>87380</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>53088</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>44169</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>96564</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>565</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>563</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>414049</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>382845</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>796895</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>399234</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>372236</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>779004</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>426079</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>392822</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>812228</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>215</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>206</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>152315</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>135455</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>287770</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>145126</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>129171</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>278243</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>157992</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>140005</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>295367</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>853</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>830</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>1683</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>617565</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>560275</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>1177840</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>601064</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>546112</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>1158313</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>631556</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>572036</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>1196305</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>